--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92791</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101561</v>
+        <v>101563</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92793</v>
+        <v>92795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -1319,7 +1319,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136793727</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136794303</v>
       </c>
       <c r="B5" t="n">
-        <v>58283</v>
+        <v>58296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136793711</v>
       </c>
       <c r="B6" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136793727</v>
       </c>
       <c r="B3" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136794303</v>
       </c>
       <c r="B5" t="n">
-        <v>58296</v>
+        <v>58298</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136793711</v>
       </c>
       <c r="B6" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
         <v>136793614</v>
       </c>
       <c r="B7" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -1131,11 +1131,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gosseholmen, Gosseholmen, Sm</t>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136793727</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136793497</v>
       </c>
       <c r="B4" t="n">
-        <v>6289</v>
+        <v>6295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136794303</v>
       </c>
       <c r="B5" t="n">
-        <v>58298</v>
+        <v>58308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136793711</v>
       </c>
       <c r="B6" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>136793614</v>
       </c>
       <c r="B7" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136793727</v>
       </c>
       <c r="B3" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136794303</v>
       </c>
       <c r="B5" t="n">
-        <v>58308</v>
+        <v>58309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136793711</v>
       </c>
       <c r="B6" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 28899-2026 artfynd.xlsx
+++ b/artfynd/A 28899-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136793854</v>
       </c>
       <c r="B2" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136793727</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136794303</v>
       </c>
       <c r="B5" t="n">
-        <v>58309</v>
+        <v>58310</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136793711</v>
       </c>
       <c r="B6" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>136793061</v>
       </c>
       <c r="B8" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
